--- a/contractor_forms/006_solar_power_quote_request_form--contractor_forms.xlsx
+++ b/contractor_forms/006_solar_power_quote_request_form--contractor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>form_submit</t>
+          <t>Form Submission</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>home_address</t>
+          <t>Home Address</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>home_city</t>
+          <t>Home City</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>home_state</t>
+          <t>Home State</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>home_zip</t>
+          <t>Home Zip</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>roof_size_sqft</t>
+          <t>Roof Size (sqft)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>roof_pitch</t>
+          <t>Roof Pitch</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>solar_panel_type</t>
+          <t>Solar Panel Type</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>solar_panel_count</t>
+          <t>Solar Panel Count</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>roof_mounting_type</t>
+          <t>Roof Mounting Type</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>installation_type</t>
+          <t>Installation Type</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>contact_name</t>
+          <t>Contact Name</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>Contact Email</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>Contact Phone</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>contact_message</t>
+          <t>Contact Message</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>form_submit</t>
+          <t>form_submit_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>form_submit</t>
+          <t>Form Submit 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>form_submit</t>
+          <t>form_submit_date</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>form_submit</t>
+          <t>Form Submission Date</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,39 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>form_submit</t>
+          <t>form_submit_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>form_submit</t>
+          <t>Form Submit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>form_submit</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>form_submit</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -960,11 +937,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -993,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1010,80 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>form_submit_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>form_submit_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>form_submit_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>form_submit_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
